--- a/m101/E101.xlsx
+++ b/m101/E101.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dragonnomada/Desktop/GitHub/diplomado-ia-asa/m101/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9E931A41-4319-9E41-B198-B7AE8DDF2511}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E7BEBD6-2051-5F4C-861F-73DD44151538}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{AA822BD8-5A04-7041-AF26-DF96B10765CC}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="1" xr2:uid="{AA822BD8-5A04-7041-AF26-DF96B10765CC}"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="Titanic" sheetId="1" r:id="rId1"/>
+    <sheet name="Pista Aerea" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="85">
   <si>
     <t>Supervivencia en el Titanic</t>
   </si>
@@ -132,12 +133,179 @@
   </si>
   <si>
     <t>P(x|m)</t>
+  </si>
+  <si>
+    <t>Liberar una pista aerea</t>
+  </si>
+  <si>
+    <t>Sin alerta</t>
+  </si>
+  <si>
+    <t>Alerta</t>
+  </si>
+  <si>
+    <t>Libre</t>
+  </si>
+  <si>
+    <t>Contaminada</t>
+  </si>
+  <si>
+    <t>P(C)</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>P(L)</t>
+  </si>
+  <si>
+    <t>P(X)</t>
+  </si>
+  <si>
+    <t>P(A)</t>
+  </si>
+  <si>
+    <t>P(C^A)</t>
+  </si>
+  <si>
+    <t>P(C^X)</t>
+  </si>
+  <si>
+    <t>P(L^A)</t>
+  </si>
+  <si>
+    <t>P(L^X)</t>
+  </si>
+  <si>
+    <t>Probabilidad Marginal</t>
+  </si>
+  <si>
+    <t>Probabilidad Conjunta</t>
+  </si>
+  <si>
+    <t>Probabilidad Condicional</t>
+  </si>
+  <si>
+    <t>Probabilidad Inversa (Bayes)</t>
+  </si>
+  <si>
+    <t>P(A|C)</t>
+  </si>
+  <si>
+    <t>P(A|L)</t>
+  </si>
+  <si>
+    <t>P(X|C)</t>
+  </si>
+  <si>
+    <t>P(X|L)</t>
+  </si>
+  <si>
+    <t>P(A|B) = P(A^B) / P(B)</t>
+  </si>
+  <si>
+    <t>P(B|A) = P(A|B) P(B) / P(A)</t>
+  </si>
+  <si>
+    <t>P(B|A) = P(A|B) P(B) / S(A + B)</t>
+  </si>
+  <si>
+    <t>P(C|A)</t>
+  </si>
+  <si>
+    <t>P(L|A)</t>
+  </si>
+  <si>
+    <t>Modelo de Utilidad Esperada (EU)</t>
+  </si>
+  <si>
+    <t>Acciones</t>
+  </si>
+  <si>
+    <t>LIBERAR</t>
+  </si>
+  <si>
+    <t>INSPECCIONAR</t>
+  </si>
+  <si>
+    <t>Estado</t>
+  </si>
+  <si>
+    <t>La alarma se activa y hay que tomar una acción</t>
+  </si>
+  <si>
+    <t>EU(LIBERAR)</t>
+  </si>
+  <si>
+    <t>EU(INSPECCIONAR)</t>
+  </si>
+  <si>
+    <t>* ESTO APLICA SOLAMENTE SOBRE MODELOS DE INCERTIDUMBRE (CUANDO NO HAY REGLAS EXPLÍCITAS PARA EVITAR IMPASSES)</t>
+  </si>
+  <si>
+    <t>P(L|A) * U1 + P(C|A) * U2</t>
+  </si>
+  <si>
+    <t>P(L|A) * V1 + P(C|A) * V2</t>
+  </si>
+  <si>
+    <t>RIESGO</t>
+  </si>
+  <si>
+    <t>ESFUERZO</t>
+  </si>
+  <si>
+    <t>UN BALANCE EFECTIVO ENTRE LA INFORMACIÓN DISPONIBLE</t>
+  </si>
+  <si>
+    <t>MAXIMIZAR LA UTILIDAD</t>
+  </si>
+  <si>
+    <t>MINIMIZAR EL RIESGO Y ESFUERZO</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>(1 - p) * U1 + p * U2</t>
+  </si>
+  <si>
+    <t>(1 - p) * U1 + p * U2 &gt; -8</t>
+  </si>
+  <si>
+    <t>p = P(C | A)</t>
+  </si>
+  <si>
+    <t>U1 - p * U1 + p * U2 &gt; -8</t>
+  </si>
+  <si>
+    <t>p(U2 - U1) &gt; -8 - U1</t>
+  </si>
+  <si>
+    <t>p &gt;</t>
+  </si>
+  <si>
+    <t>p &gt; -(8 + U1) / (U2 - U1)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="0.000%"/>
+    <numFmt numFmtId="168" formatCode="0.0"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -154,15 +322,33 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -199,14 +385,57 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -216,6 +445,39 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="168" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -589,10 +851,10 @@
       <c r="C7" t="s">
         <v>4</v>
       </c>
-      <c r="D7" s="1">
+      <c r="D7">
         <v>40</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="2">
         <v>250</v>
       </c>
       <c r="F7">
@@ -607,10 +869,10 @@
       <c r="C8" t="s">
         <v>5</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="1">
         <v>420</v>
       </c>
-      <c r="E8" s="4">
+      <c r="E8" s="3">
         <v>70</v>
       </c>
       <c r="F8">
@@ -636,14 +898,14 @@
       <c r="D12" t="s">
         <v>10</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E12" s="4">
         <f>D9/G8</f>
         <v>0.58974358974358976</v>
       </c>
       <c r="G12" t="s">
         <v>14</v>
       </c>
-      <c r="H12" s="5">
+      <c r="H12" s="4">
         <f>E26/E12</f>
         <v>8.6956521739130432E-2</v>
       </c>
@@ -652,14 +914,14 @@
       <c r="D13" t="s">
         <v>11</v>
       </c>
-      <c r="E13" s="5">
+      <c r="E13" s="4">
         <f>E9/G8</f>
         <v>0.41025641025641024</v>
       </c>
       <c r="G13" t="s">
         <v>15</v>
       </c>
-      <c r="H13" s="5">
+      <c r="H13" s="4">
         <f>E28/E13</f>
         <v>0.78125000000000011</v>
       </c>
@@ -668,14 +930,14 @@
       <c r="D15" t="s">
         <v>12</v>
       </c>
-      <c r="E15" s="5">
+      <c r="E15" s="4">
         <f>F7/G8</f>
         <v>0.37179487179487181</v>
       </c>
       <c r="G15" t="s">
         <v>22</v>
       </c>
-      <c r="H15" s="5">
+      <c r="H15" s="4">
         <f>E27/E12</f>
         <v>0.91304347826086951</v>
       </c>
@@ -684,14 +946,14 @@
       <c r="D16" t="s">
         <v>13</v>
       </c>
-      <c r="E16" s="5">
+      <c r="E16" s="4">
         <f>F8/G8</f>
         <v>0.62820512820512819</v>
       </c>
       <c r="G16" t="s">
         <v>23</v>
       </c>
-      <c r="H16" s="5">
+      <c r="H16" s="4">
         <f>E29/E13</f>
         <v>0.21875</v>
       </c>
@@ -725,11 +987,11 @@
       <c r="C21" t="s">
         <v>4</v>
       </c>
-      <c r="D21" s="6">
+      <c r="D21" s="5">
         <f>D7/G8</f>
         <v>5.128205128205128E-2</v>
       </c>
-      <c r="E21" s="7">
+      <c r="E21" s="6">
         <f>E7/G8</f>
         <v>0.32051282051282054</v>
       </c>
@@ -738,11 +1000,11 @@
       <c r="C22" t="s">
         <v>5</v>
       </c>
-      <c r="D22" s="8">
+      <c r="D22" s="7">
         <f>D8/G8</f>
         <v>0.53846153846153844</v>
       </c>
-      <c r="E22" s="9">
+      <c r="E22" s="8">
         <f>E8/G8</f>
         <v>8.9743589743589744E-2</v>
       </c>
@@ -751,7 +1013,7 @@
       <c r="G23" t="s">
         <v>24</v>
       </c>
-      <c r="H23" s="5">
+      <c r="H23" s="4">
         <f>H12*E15/E12</f>
         <v>5.4820415879017016E-2</v>
       </c>
@@ -763,7 +1025,7 @@
       <c r="G24" t="s">
         <v>28</v>
       </c>
-      <c r="H24" s="5">
+      <c r="H24" s="4">
         <f>H13*E15/E13</f>
         <v>0.70800781250000011</v>
       </c>
@@ -772,14 +1034,14 @@
       <c r="D26" t="s">
         <v>17</v>
       </c>
-      <c r="E26" s="10">
+      <c r="E26" s="9">
         <f>D21</f>
         <v>5.128205128205128E-2</v>
       </c>
       <c r="G26" t="s">
         <v>29</v>
       </c>
-      <c r="H26" s="5">
+      <c r="H26" s="4">
         <f>H15*E16/E12</f>
         <v>0.97258979206049134</v>
       </c>
@@ -788,14 +1050,14 @@
       <c r="D27" t="s">
         <v>18</v>
       </c>
-      <c r="E27" s="10">
+      <c r="E27" s="9">
         <f>D22</f>
         <v>0.53846153846153844</v>
       </c>
       <c r="G27" t="s">
         <v>30</v>
       </c>
-      <c r="H27" s="5">
+      <c r="H27" s="4">
         <f>H16*E16/E13</f>
         <v>0.33496093750000006</v>
       </c>
@@ -804,7 +1066,7 @@
       <c r="D28" t="s">
         <v>19</v>
       </c>
-      <c r="E28" s="10">
+      <c r="E28" s="9">
         <f>E21</f>
         <v>0.32051282051282054</v>
       </c>
@@ -813,7 +1075,7 @@
       <c r="D29" t="s">
         <v>20</v>
       </c>
-      <c r="E29" s="10">
+      <c r="E29" s="9">
         <f>E22</f>
         <v>8.9743589743589744E-2</v>
       </c>
@@ -829,4 +1091,610 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC606130-A7BC-A641-B2E3-F87555B7A989}">
+  <dimension ref="B2:Q48"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="4" max="4" width="13.6640625" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="7" max="7" width="13.6640625" customWidth="1"/>
+    <col min="8" max="8" width="13.33203125" customWidth="1"/>
+    <col min="10" max="10" width="20.83203125" customWidth="1"/>
+    <col min="12" max="12" width="17" customWidth="1"/>
+    <col min="13" max="13" width="14.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B2" t="s">
+        <v>31</v>
+      </c>
+      <c r="J2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="D4" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="D5" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="K5" t="s">
+        <v>62</v>
+      </c>
+      <c r="L5" t="s">
+        <v>63</v>
+      </c>
+      <c r="M5" t="s">
+        <v>64</v>
+      </c>
+      <c r="O5" s="23" t="s">
+        <v>74</v>
+      </c>
+      <c r="P5" s="23"/>
+      <c r="Q5" s="23"/>
+    </row>
+    <row r="6" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B6" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6">
+        <f>980-E7</f>
+        <v>931</v>
+      </c>
+      <c r="F6">
+        <f>SUM(D6:E6)</f>
+        <v>933</v>
+      </c>
+      <c r="J6" t="s">
+        <v>65</v>
+      </c>
+      <c r="O6" s="23"/>
+      <c r="P6" s="23"/>
+      <c r="Q6" s="23"/>
+    </row>
+    <row r="7" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B7" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7">
+        <v>18</v>
+      </c>
+      <c r="E7">
+        <v>49</v>
+      </c>
+      <c r="F7">
+        <f>SUM(D7:E7)</f>
+        <v>67</v>
+      </c>
+      <c r="O7" s="23"/>
+      <c r="P7" s="23"/>
+      <c r="Q7" s="23"/>
+    </row>
+    <row r="8" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="D8">
+        <f>SUM(D6:D7)</f>
+        <v>20</v>
+      </c>
+      <c r="E8">
+        <f>SUM(E6:E7)</f>
+        <v>980</v>
+      </c>
+      <c r="F8">
+        <f>SUM(D6:E7)</f>
+        <v>1000</v>
+      </c>
+      <c r="J8" t="s">
+        <v>35</v>
+      </c>
+      <c r="L8">
+        <v>-1000</v>
+      </c>
+      <c r="M8">
+        <v>-8</v>
+      </c>
+    </row>
+    <row r="9" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="J9" t="s">
+        <v>34</v>
+      </c>
+      <c r="L9">
+        <v>10</v>
+      </c>
+      <c r="M9">
+        <v>-8</v>
+      </c>
+      <c r="O9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="10" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="D10" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="E10" s="13"/>
+      <c r="G10" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="H10" s="13"/>
+      <c r="O10" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="11" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="J11" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="K11" s="21"/>
+      <c r="L11" s="21"/>
+      <c r="M11" s="21"/>
+    </row>
+    <row r="12" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="D12" t="s">
+        <v>36</v>
+      </c>
+      <c r="E12" s="20">
+        <f>D8/F8</f>
+        <v>0.02</v>
+      </c>
+      <c r="G12" t="s">
+        <v>44</v>
+      </c>
+      <c r="H12" s="12">
+        <f>D7/F8</f>
+        <v>1.7999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="D13" t="s">
+        <v>41</v>
+      </c>
+      <c r="E13" s="12">
+        <f>E8/F8</f>
+        <v>0.98</v>
+      </c>
+      <c r="G13" t="s">
+        <v>45</v>
+      </c>
+      <c r="H13" s="12">
+        <f>D6/F8</f>
+        <v>2E-3</v>
+      </c>
+      <c r="J13" t="s">
+        <v>59</v>
+      </c>
+      <c r="K13" s="15">
+        <v>0.26900000000000002</v>
+      </c>
+    </row>
+    <row r="14" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="E14" s="12"/>
+      <c r="H14" s="12"/>
+      <c r="J14" t="s">
+        <v>60</v>
+      </c>
+      <c r="K14" s="15">
+        <v>0.73099999999999998</v>
+      </c>
+    </row>
+    <row r="15" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="D15" t="s">
+        <v>42</v>
+      </c>
+      <c r="E15" s="12">
+        <f>F6/F8</f>
+        <v>0.93300000000000005</v>
+      </c>
+      <c r="G15" t="s">
+        <v>46</v>
+      </c>
+      <c r="H15" s="12">
+        <f>E7/F8</f>
+        <v>4.9000000000000002E-2</v>
+      </c>
+      <c r="O15" t="s">
+        <v>72</v>
+      </c>
+      <c r="P15" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="16" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="D16" t="s">
+        <v>43</v>
+      </c>
+      <c r="E16" s="12">
+        <f>F7/F8</f>
+        <v>6.7000000000000004E-2</v>
+      </c>
+      <c r="G16" t="s">
+        <v>47</v>
+      </c>
+      <c r="H16" s="12">
+        <f>E6/F8</f>
+        <v>0.93100000000000005</v>
+      </c>
+    </row>
+    <row r="17" spans="4:16" x14ac:dyDescent="0.2">
+      <c r="J17" t="s">
+        <v>67</v>
+      </c>
+      <c r="K17" s="26">
+        <f>K14*L9 + K13*L8</f>
+        <v>-261.69</v>
+      </c>
+      <c r="L17" s="25" t="s">
+        <v>70</v>
+      </c>
+      <c r="M17" s="25"/>
+      <c r="O17" s="15">
+        <v>0.26900000000000002</v>
+      </c>
+      <c r="P17" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="4:16" x14ac:dyDescent="0.2">
+      <c r="D18" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="E18" s="13"/>
+      <c r="G18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J18" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="K18" s="27">
+        <f>K14*M9 + K13*M8</f>
+        <v>-8</v>
+      </c>
+      <c r="L18" s="25" t="s">
+        <v>71</v>
+      </c>
+      <c r="M18" s="25"/>
+      <c r="O18" s="9">
+        <v>0</v>
+      </c>
+      <c r="P18" s="9">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="19" spans="4:16" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="20" spans="4:16" x14ac:dyDescent="0.2">
+      <c r="D20" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="E20" s="17">
+        <f>H12/E12</f>
+        <v>0.89999999999999991</v>
+      </c>
+      <c r="G20" t="s">
+        <v>59</v>
+      </c>
+      <c r="H20" s="20">
+        <f>E20*E12/E16</f>
+        <v>0.26865671641791039</v>
+      </c>
+    </row>
+    <row r="21" spans="4:16" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="D21" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="E21" s="19">
+        <f>H15/E13</f>
+        <v>0.05</v>
+      </c>
+      <c r="G21" t="s">
+        <v>60</v>
+      </c>
+      <c r="H21" s="12">
+        <f>E21*E13/E16</f>
+        <v>0.73134328358208955</v>
+      </c>
+      <c r="J21" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="K21" s="24"/>
+      <c r="L21" s="24"/>
+      <c r="M21" s="24"/>
+    </row>
+    <row r="22" spans="4:16" x14ac:dyDescent="0.2">
+      <c r="J22" s="24"/>
+      <c r="K22" s="24"/>
+      <c r="L22" s="24"/>
+      <c r="M22" s="24"/>
+    </row>
+    <row r="23" spans="4:16" x14ac:dyDescent="0.2">
+      <c r="D23" t="s">
+        <v>54</v>
+      </c>
+      <c r="E23" s="14">
+        <f>H13/E12</f>
+        <v>0.1</v>
+      </c>
+      <c r="J23" s="24"/>
+      <c r="K23" s="24"/>
+      <c r="L23" s="24"/>
+      <c r="M23" s="24"/>
+    </row>
+    <row r="24" spans="4:16" x14ac:dyDescent="0.2">
+      <c r="D24" t="s">
+        <v>55</v>
+      </c>
+      <c r="E24" s="4">
+        <f>H16/E13</f>
+        <v>0.95000000000000007</v>
+      </c>
+      <c r="J24" s="24"/>
+      <c r="K24" s="24"/>
+      <c r="L24" s="24"/>
+      <c r="M24" s="24"/>
+    </row>
+    <row r="26" spans="4:16" x14ac:dyDescent="0.2">
+      <c r="N26" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="27" spans="4:16" x14ac:dyDescent="0.2">
+      <c r="D27" t="s">
+        <v>56</v>
+      </c>
+      <c r="G27" t="s">
+        <v>57</v>
+      </c>
+      <c r="K27" t="s">
+        <v>77</v>
+      </c>
+      <c r="L27" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="28" spans="4:16" x14ac:dyDescent="0.2">
+      <c r="K28" s="4">
+        <v>0</v>
+      </c>
+      <c r="L28">
+        <f>(1-K28)*$L$9+K28*$L$8</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" spans="4:16" x14ac:dyDescent="0.2">
+      <c r="G29" t="s">
+        <v>58</v>
+      </c>
+      <c r="K29" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="L29">
+        <f t="shared" ref="L29:L48" si="0">(1-K29)*$L$9+K29*$L$8</f>
+        <v>-40.5</v>
+      </c>
+      <c r="N29">
+        <v>-8</v>
+      </c>
+    </row>
+    <row r="30" spans="4:16" x14ac:dyDescent="0.2">
+      <c r="K30" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="L30">
+        <f t="shared" si="0"/>
+        <v>-91</v>
+      </c>
+    </row>
+    <row r="31" spans="4:16" x14ac:dyDescent="0.2">
+      <c r="K31" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="L31">
+        <f t="shared" si="0"/>
+        <v>-141.5</v>
+      </c>
+      <c r="N31" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="32" spans="4:16" x14ac:dyDescent="0.2">
+      <c r="K32" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="L32">
+        <f t="shared" si="0"/>
+        <v>-192</v>
+      </c>
+    </row>
+    <row r="33" spans="11:15" x14ac:dyDescent="0.2">
+      <c r="K33" s="4">
+        <v>0.25</v>
+      </c>
+      <c r="L33">
+        <f t="shared" si="0"/>
+        <v>-242.5</v>
+      </c>
+      <c r="N33" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="34" spans="11:15" x14ac:dyDescent="0.2">
+      <c r="K34" s="4">
+        <v>0.3</v>
+      </c>
+      <c r="L34">
+        <f t="shared" si="0"/>
+        <v>-293</v>
+      </c>
+    </row>
+    <row r="35" spans="11:15" x14ac:dyDescent="0.2">
+      <c r="K35" s="4">
+        <v>0.35</v>
+      </c>
+      <c r="L35">
+        <f t="shared" si="0"/>
+        <v>-343.5</v>
+      </c>
+      <c r="N35" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="36" spans="11:15" x14ac:dyDescent="0.2">
+      <c r="K36" s="4">
+        <v>0.4</v>
+      </c>
+      <c r="L36">
+        <f t="shared" si="0"/>
+        <v>-394</v>
+      </c>
+    </row>
+    <row r="37" spans="11:15" x14ac:dyDescent="0.2">
+      <c r="K37" s="4">
+        <v>0.45</v>
+      </c>
+      <c r="L37">
+        <f t="shared" si="0"/>
+        <v>-444.5</v>
+      </c>
+      <c r="N37" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="38" spans="11:15" x14ac:dyDescent="0.2">
+      <c r="K38" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="L38">
+        <f t="shared" si="0"/>
+        <v>-495</v>
+      </c>
+    </row>
+    <row r="39" spans="11:15" x14ac:dyDescent="0.2">
+      <c r="K39" s="4">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="L39">
+        <f t="shared" si="0"/>
+        <v>-545.5</v>
+      </c>
+      <c r="N39" t="s">
+        <v>83</v>
+      </c>
+      <c r="O39" s="28">
+        <f>(8 + 10) / (10 + 1000)</f>
+        <v>1.782178217821782E-2</v>
+      </c>
+    </row>
+    <row r="40" spans="11:15" x14ac:dyDescent="0.2">
+      <c r="K40" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="L40">
+        <f t="shared" si="0"/>
+        <v>-596</v>
+      </c>
+    </row>
+    <row r="41" spans="11:15" x14ac:dyDescent="0.2">
+      <c r="K41" s="4">
+        <v>0.65</v>
+      </c>
+      <c r="L41">
+        <f t="shared" si="0"/>
+        <v>-646.5</v>
+      </c>
+    </row>
+    <row r="42" spans="11:15" x14ac:dyDescent="0.2">
+      <c r="K42" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="L42">
+        <f t="shared" si="0"/>
+        <v>-697</v>
+      </c>
+    </row>
+    <row r="43" spans="11:15" x14ac:dyDescent="0.2">
+      <c r="K43" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="L43">
+        <f t="shared" si="0"/>
+        <v>-747.5</v>
+      </c>
+    </row>
+    <row r="44" spans="11:15" x14ac:dyDescent="0.2">
+      <c r="K44" s="4">
+        <v>0.8</v>
+      </c>
+      <c r="L44">
+        <f t="shared" si="0"/>
+        <v>-798</v>
+      </c>
+    </row>
+    <row r="45" spans="11:15" x14ac:dyDescent="0.2">
+      <c r="K45" s="4">
+        <v>0.85</v>
+      </c>
+      <c r="L45">
+        <f t="shared" si="0"/>
+        <v>-848.5</v>
+      </c>
+    </row>
+    <row r="46" spans="11:15" x14ac:dyDescent="0.2">
+      <c r="K46" s="4">
+        <v>0.9</v>
+      </c>
+      <c r="L46">
+        <f t="shared" si="0"/>
+        <v>-899</v>
+      </c>
+    </row>
+    <row r="47" spans="11:15" x14ac:dyDescent="0.2">
+      <c r="K47" s="4">
+        <v>0.95</v>
+      </c>
+      <c r="L47">
+        <f t="shared" si="0"/>
+        <v>-949.5</v>
+      </c>
+    </row>
+    <row r="48" spans="11:15" x14ac:dyDescent="0.2">
+      <c r="K48" s="4">
+        <v>1</v>
+      </c>
+      <c r="L48">
+        <f t="shared" si="0"/>
+        <v>-1000</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="O5:Q7"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="J11:M11"/>
+    <mergeCell ref="J21:M24"/>
+    <mergeCell ref="L17:M17"/>
+    <mergeCell ref="L18:M18"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>